--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636563</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136636569</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136636566</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>136636571</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>136636558</v>
       </c>
       <c r="B13" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636563</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136636569</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136636566</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>136636571</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>136636558</v>
       </c>
       <c r="B13" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18648-2025 artfynd.xlsx
+++ b/artfynd/A 18648-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636562</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636565</v>
       </c>
       <c r="B3" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636570</v>
       </c>
       <c r="B4" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636573</v>
       </c>
       <c r="B5" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636561</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636572</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636563</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136636569</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136636566</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>136636571</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>136636558</v>
       </c>
       <c r="B13" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136636564</v>
       </c>
       <c r="B14" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
